--- a/data/trans_orig/P19-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2007</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135355</t>
+          <t>136386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182395</t>
+          <t>179141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192098</t>
+          <t>190383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238205</t>
+          <t>238359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>339510</t>
+          <t>338421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>406561</t>
+          <t>402328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>511617</t>
+          <t>514871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>558657</t>
+          <t>557626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>449221</t>
+          <t>449067</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>495328</t>
+          <t>497043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>974877</t>
+          <t>979110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1041928</t>
+          <t>1043017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>214253</t>
+          <t>212528</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>267705</t>
+          <t>271050</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>275711</t>
+          <t>278174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>337371</t>
+          <t>335381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>502517</t>
+          <t>501966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>586132</t>
+          <t>583663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>694095</t>
+          <t>690750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>747547</t>
+          <t>749272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>631022</t>
+          <t>633012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>692682</t>
+          <t>690219</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1344061</t>
+          <t>1346530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1427676</t>
+          <t>1428227</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164171</t>
+          <t>163129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209806</t>
+          <t>211194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>196449</t>
+          <t>199749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>246751</t>
+          <t>248273</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374246</t>
+          <t>374201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>442293</t>
+          <t>443114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468703</t>
+          <t>467315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>514338</t>
+          <t>515380</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437090</t>
+          <t>435568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>487392</t>
+          <t>484092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>920057</t>
+          <t>919236</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>988104</t>
+          <t>988149</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206731</t>
+          <t>206496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257358</t>
+          <t>258784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>290458</t>
+          <t>288558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>353136</t>
+          <t>349888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>509991</t>
+          <t>511381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>588553</t>
+          <t>590955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>683952</t>
+          <t>682526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>734579</t>
+          <t>734814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>685476</t>
+          <t>688724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>748154</t>
+          <t>750054</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1391369</t>
+          <t>1388967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1469931</t>
+          <t>1468541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>761136</t>
+          <t>765770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>862782</t>
+          <t>869320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1006886</t>
+          <t>1006060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1110122</t>
+          <t>1115428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1798612</t>
+          <t>1794572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1942870</t>
+          <t>1949930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2412849</t>
+          <t>2406311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2514495</t>
+          <t>2509861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2268150</t>
+          <t>2262844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2371386</t>
+          <t>2372212</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4711034</t>
+          <t>4703974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4855292</t>
+          <t>4859332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2012</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134285</t>
+          <t>133552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176928</t>
+          <t>176324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>181723</t>
+          <t>181462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230500</t>
+          <t>230697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>330869</t>
+          <t>331792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>395532</t>
+          <t>399479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>524028</t>
+          <t>524632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>566671</t>
+          <t>567404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>466550</t>
+          <t>466353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>515327</t>
+          <t>515588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1002474</t>
+          <t>998527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1067137</t>
+          <t>1066214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>212598</t>
+          <t>213975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>271091</t>
+          <t>270496</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>282464</t>
+          <t>283127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>345862</t>
+          <t>343670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>510520</t>
+          <t>514335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>595649</t>
+          <t>599599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>746856</t>
+          <t>747451</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>805349</t>
+          <t>803972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>686322</t>
+          <t>688514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>749720</t>
+          <t>749057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1454482</t>
+          <t>1450532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1539611</t>
+          <t>1535796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,91%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177067</t>
+          <t>174683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>228681</t>
+          <t>226394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203336</t>
+          <t>200895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255186</t>
+          <t>254349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>393344</t>
+          <t>390148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>465793</t>
+          <t>464557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528942</t>
+          <t>531229</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>580556</t>
+          <t>582940</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521988</t>
+          <t>522825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>573838</t>
+          <t>576279</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1069004</t>
+          <t>1070240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1141453</t>
+          <t>1144649</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>218821</t>
+          <t>220419</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>274952</t>
+          <t>277651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,47 +3724,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>29,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>334364</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>304863</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>368761</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>29,01%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>334364</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>304014</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>365290</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>28,93%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>540250</t>
+          <t>540460</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>621748</t>
+          <t>627770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>672787</t>
+          <t>670088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>728918</t>
+          <t>727320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,49 +3837,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>70,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>716573</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>682176</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>746074</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>68,18%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>64,91%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>70,99%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>76,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>716573</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>685647</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>746923</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>68,18%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>71,07%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1359</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1376928</t>
+          <t>1370906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1458426</t>
+          <t>1458216</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>793371</t>
+          <t>795892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>893185</t>
+          <t>897514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1026159</t>
+          <t>1018088</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1139075</t>
+          <t>1129440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1849388</t>
+          <t>1844792</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2002245</t>
+          <t>1998460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2531081</t>
+          <t>2526752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2630895</t>
+          <t>2628374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2418270</t>
+          <t>2427905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2531186</t>
+          <t>2539257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4979365</t>
+          <t>4983150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5132222</t>
+          <t>5136818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2016</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169433</t>
+          <t>170751</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>217101</t>
+          <t>217257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207036</t>
+          <t>209527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>254953</t>
+          <t>255873</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>391416</t>
+          <t>389663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>456678</t>
+          <t>457278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457699</t>
+          <t>457543</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>505367</t>
+          <t>504049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>417886</t>
+          <t>416966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>465803</t>
+          <t>463312</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>890961</t>
+          <t>890361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>956223</t>
+          <t>957976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>258971</t>
+          <t>259754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>319807</t>
+          <t>321164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>338930</t>
+          <t>338116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>403250</t>
+          <t>405949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>617722</t>
+          <t>616432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>708165</t>
+          <t>704721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>702624</t>
+          <t>701267</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>763460</t>
+          <t>762677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>639663</t>
+          <t>636964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>703983</t>
+          <t>704797</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1357179</t>
+          <t>1360623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1447622</t>
+          <t>1448912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>211263</t>
+          <t>209729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>266236</t>
+          <t>264067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>247693</t>
+          <t>245577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>299408</t>
+          <t>299651</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>471213</t>
+          <t>475053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>547244</t>
+          <t>552450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>493316</t>
+          <t>495485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>548289</t>
+          <t>549823</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>485603</t>
+          <t>485360</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537318</t>
+          <t>539434</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>997319</t>
+          <t>992113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073350</t>
+          <t>1069510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239247</t>
+          <t>239095</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>300205</t>
+          <t>294736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>316604</t>
+          <t>309936</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>376236</t>
+          <t>375599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>572789</t>
+          <t>574242</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>656800</t>
+          <t>655447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637362</t>
+          <t>642831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>698320</t>
+          <t>698472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>667543</t>
+          <t>668180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>727175</t>
+          <t>733843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1324546</t>
+          <t>1325899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1408557</t>
+          <t>1407104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>927665</t>
+          <t>934257</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1038411</t>
+          <t>1035721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1165881</t>
+          <t>1168344</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1279347</t>
+          <t>1281496</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2120052</t>
+          <t>2131619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2285927</t>
+          <t>2290065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2355939</t>
+          <t>2358629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2466685</t>
+          <t>2460093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2265195</t>
+          <t>2263046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2378661</t>
+          <t>2376198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4652965</t>
+          <t>4648827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4818840</t>
+          <t>4807273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 6 meses han ido al dentista en 2023</t>
+          <t>Población según si en los últimos 6 meses han ido al dentista en 2023 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121479</t>
+          <t>121179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>170899</t>
+          <t>168443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178620</t>
+          <t>178203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>218945</t>
+          <t>217869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308946</t>
+          <t>308369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>372505</t>
+          <t>374740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>461923</t>
+          <t>464379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>511343</t>
+          <t>511643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>452623</t>
+          <t>453699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>492948</t>
+          <t>493365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>931885</t>
+          <t>929650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>995444</t>
+          <t>996021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125554</t>
+          <t>128966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>300925</t>
+          <t>301943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240642</t>
+          <t>239349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>288716</t>
+          <t>289291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>326505</t>
+          <t>335620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>571336</t>
+          <t>570800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>885371</t>
+          <t>884353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1060742</t>
+          <t>1057330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>665701</t>
+          <t>665126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>713775</t>
+          <t>715068</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1569377</t>
+          <t>1569913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1814208</t>
+          <t>1805093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>197306</t>
+          <t>196684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255426</t>
+          <t>254540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>138411</t>
+          <t>136661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>364811</t>
+          <t>368118</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320149</t>
+          <t>336680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>584068</t>
+          <t>591882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>448378</t>
+          <t>449264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506498</t>
+          <t>507120</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>561215</t>
+          <t>557908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>787615</t>
+          <t>789365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1045762</t>
+          <t>1037948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1309681</t>
+          <t>1293150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>237497</t>
+          <t>236010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>296714</t>
+          <t>296309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>281963</t>
+          <t>283610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>390591</t>
+          <t>388081</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>537525</t>
+          <t>546922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>666471</t>
+          <t>667310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616896</t>
+          <t>617301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>676113</t>
+          <t>677600</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>687212</t>
+          <t>689722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>795840</t>
+          <t>794193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1324942</t>
+          <t>1324103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453888</t>
+          <t>1444491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,54%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>650025</t>
+          <t>669893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>952093</t>
+          <t>947806</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>878391</t>
+          <t>884215</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1189142</t>
+          <t>1187018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1715635</t>
+          <t>1673995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2097718</t>
+          <t>2093062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2484439</t>
+          <t>2488726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2786507</t>
+          <t>2766639</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2440672</t>
+          <t>2442796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2751423</t>
+          <t>2745599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4968628</t>
+          <t>4973284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5350711</t>
+          <t>5392351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136386</t>
+          <t>136825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179141</t>
+          <t>178516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190383</t>
+          <t>187906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238359</t>
+          <t>237271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>338421</t>
+          <t>339673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>402328</t>
+          <t>403447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>514871</t>
+          <t>515496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>557626</t>
+          <t>557187</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>449067</t>
+          <t>450155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>497043</t>
+          <t>499520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>979110</t>
+          <t>977991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1043017</t>
+          <t>1041765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>212528</t>
+          <t>212791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>271050</t>
+          <t>267282</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>278174</t>
+          <t>275452</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>335381</t>
+          <t>335151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>501966</t>
+          <t>504295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>583663</t>
+          <t>582598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>690750</t>
+          <t>694518</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>749272</t>
+          <t>749009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>633012</t>
+          <t>633242</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>690219</t>
+          <t>692941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1346530</t>
+          <t>1347595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1428227</t>
+          <t>1425898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163129</t>
+          <t>163029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211194</t>
+          <t>211354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199749</t>
+          <t>199287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248273</t>
+          <t>245634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374201</t>
+          <t>377435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>443114</t>
+          <t>443764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>467315</t>
+          <t>467155</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515380</t>
+          <t>515480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>435568</t>
+          <t>438207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>484092</t>
+          <t>484554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>919236</t>
+          <t>918586</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>988149</t>
+          <t>984915</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206496</t>
+          <t>205320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258784</t>
+          <t>260121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288558</t>
+          <t>286961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>349888</t>
+          <t>346675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>511381</t>
+          <t>511264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>590955</t>
+          <t>590882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>682526</t>
+          <t>681189</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>734814</t>
+          <t>735990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>688724</t>
+          <t>691937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>750054</t>
+          <t>751651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1388967</t>
+          <t>1389040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1468541</t>
+          <t>1468658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,18%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>767116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>869320</t>
+          <t>869016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1006060</t>
+          <t>1007614</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1115428</t>
+          <t>1115681</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1794572</t>
+          <t>1806499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1949930</t>
+          <t>1946168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2406311</t>
+          <t>2406615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2509861</t>
+          <t>2508515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2262844</t>
+          <t>2262591</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2372212</t>
+          <t>2370658</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4703974</t>
+          <t>4707736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4859332</t>
+          <t>4847405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133552</t>
+          <t>132786</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176324</t>
+          <t>179147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>181462</t>
+          <t>181114</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230697</t>
+          <t>231558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>331792</t>
+          <t>327030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>399479</t>
+          <t>395668</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>524632</t>
+          <t>521809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>567404</t>
+          <t>568170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>466353</t>
+          <t>465492</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>515588</t>
+          <t>515936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>998527</t>
+          <t>1002338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1066214</t>
+          <t>1070976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>213975</t>
+          <t>214192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>270496</t>
+          <t>267027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>283127</t>
+          <t>282129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>343670</t>
+          <t>342202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>514335</t>
+          <t>509892</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>599599</t>
+          <t>592258</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>747451</t>
+          <t>750920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>803972</t>
+          <t>803755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>688514</t>
+          <t>689982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>749057</t>
+          <t>750055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1450532</t>
+          <t>1457873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1535796</t>
+          <t>1540239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,13%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174683</t>
+          <t>177047</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>226394</t>
+          <t>228150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200895</t>
+          <t>199892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>254349</t>
+          <t>252101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390148</t>
+          <t>392436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>464557</t>
+          <t>467317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531229</t>
+          <t>529473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>582940</t>
+          <t>580576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>522825</t>
+          <t>525073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>576279</t>
+          <t>577282</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1070240</t>
+          <t>1067480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1144649</t>
+          <t>1142361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220419</t>
+          <t>218753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277651</t>
+          <t>275476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>304863</t>
+          <t>307056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>368761</t>
+          <t>365865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>540460</t>
+          <t>539541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>627770</t>
+          <t>626297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>670088</t>
+          <t>672263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>727320</t>
+          <t>728986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682176</t>
+          <t>685072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746074</t>
+          <t>743881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1370906</t>
+          <t>1372379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1458216</t>
+          <t>1459135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>795892</t>
+          <t>793953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>897514</t>
+          <t>900175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1018088</t>
+          <t>1019104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1129440</t>
+          <t>1132904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1844792</t>
+          <t>1846546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1998460</t>
+          <t>2001610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2526752</t>
+          <t>2524091</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2628374</t>
+          <t>2630313</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2427905</t>
+          <t>2424441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2539257</t>
+          <t>2538241</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4983150</t>
+          <t>4980000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5136818</t>
+          <t>5135064</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170751</t>
+          <t>169652</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>217257</t>
+          <t>214735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>209527</t>
+          <t>207958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>255873</t>
+          <t>255467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>389663</t>
+          <t>390421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>457278</t>
+          <t>457918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>457543</t>
+          <t>460065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504049</t>
+          <t>505148</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>416966</t>
+          <t>417372</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>463312</t>
+          <t>464881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>890361</t>
+          <t>889721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>957976</t>
+          <t>957218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>259754</t>
+          <t>256581</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>321164</t>
+          <t>314504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>338116</t>
+          <t>340138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>405949</t>
+          <t>407512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>616432</t>
+          <t>620288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>704721</t>
+          <t>706927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701267</t>
+          <t>707927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>762677</t>
+          <t>765850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>636964</t>
+          <t>635401</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>704797</t>
+          <t>702775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1360623</t>
+          <t>1358417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1448912</t>
+          <t>1445056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>209729</t>
+          <t>211275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>264067</t>
+          <t>262944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>245577</t>
+          <t>251123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>299651</t>
+          <t>302159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>475053</t>
+          <t>474297</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>552450</t>
+          <t>548524</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495485</t>
+          <t>496608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549823</t>
+          <t>548277</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>485360</t>
+          <t>482852</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539434</t>
+          <t>533888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>992113</t>
+          <t>996039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069510</t>
+          <t>1070266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239095</t>
+          <t>242530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294736</t>
+          <t>298293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>309936</t>
+          <t>316123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>375599</t>
+          <t>376568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>574242</t>
+          <t>573201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>655447</t>
+          <t>657605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>642831</t>
+          <t>639274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>698472</t>
+          <t>695037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>668180</t>
+          <t>667211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733843</t>
+          <t>727656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1325899</t>
+          <t>1323741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1407104</t>
+          <t>1408145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>934257</t>
+          <t>939015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1035721</t>
+          <t>1038925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1168344</t>
+          <t>1167396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1281496</t>
+          <t>1283111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2131619</t>
+          <t>2129771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2290065</t>
+          <t>2289983</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2358629</t>
+          <t>2355425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2460093</t>
+          <t>2455335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2263046</t>
+          <t>2261431</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2376198</t>
+          <t>2377146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4648827</t>
+          <t>4648909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4807273</t>
+          <t>4809121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>143302</t>
+          <t>152490</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121179</t>
+          <t>126516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168443</t>
+          <t>175314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>197393</t>
+          <t>209704</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178203</t>
+          <t>189589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217869</t>
+          <t>231211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>340695</t>
+          <t>362194</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308369</t>
+          <t>331346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>374740</t>
+          <t>394973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>489520</t>
+          <t>535039</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464379</t>
+          <t>512215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>511643</t>
+          <t>561013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>474175</t>
+          <t>519207</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>453699</t>
+          <t>497700</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>493365</t>
+          <t>539322</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>963695</t>
+          <t>1054246</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>929650</t>
+          <t>1021467</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>996021</t>
+          <t>1085094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>632822</t>
+          <t>687529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>632822</t>
+          <t>687529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>632822</t>
+          <t>687529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>671568</t>
+          <t>728911</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>671568</t>
+          <t>728911</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>671568</t>
+          <t>728911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1304390</t>
+          <t>1416440</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1304390</t>
+          <t>1416440</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1304390</t>
+          <t>1416440</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>229713</t>
+          <t>248542</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128966</t>
+          <t>216748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>301943</t>
+          <t>279819</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>263841</t>
+          <t>289686</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239349</t>
+          <t>264295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289291</t>
+          <t>316715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>493554</t>
+          <t>538227</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>335620</t>
+          <t>499166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>570800</t>
+          <t>580730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>956583</t>
+          <t>792805</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>884353</t>
+          <t>761528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1057330</t>
+          <t>824599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>690576</t>
+          <t>777128</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>665126</t>
+          <t>750099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>715068</t>
+          <t>802519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1647159</t>
+          <t>1569934</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1569913</t>
+          <t>1527431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1805093</t>
+          <t>1608995</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>76,32%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1186296</t>
+          <t>1041347</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1186296</t>
+          <t>1041347</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1186296</t>
+          <t>1041347</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>954417</t>
+          <t>1066814</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>954417</t>
+          <t>1066814</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>954417</t>
+          <t>1066814</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2140713</t>
+          <t>2108161</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2140713</t>
+          <t>2108161</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2140713</t>
+          <t>2108161</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>224665</t>
+          <t>240379</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>196684</t>
+          <t>211386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>254540</t>
+          <t>271568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>268809</t>
+          <t>270402</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136661</t>
+          <t>246834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>368118</t>
+          <t>295007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>493474</t>
+          <t>510781</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>336680</t>
+          <t>472887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>591882</t>
+          <t>549167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>479139</t>
+          <t>561768</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>449264</t>
+          <t>530579</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>507120</t>
+          <t>590761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>657217</t>
+          <t>533389</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>557908</t>
+          <t>508784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>789365</t>
+          <t>556957</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1136356</t>
+          <t>1095158</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1037948</t>
+          <t>1056772</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293150</t>
+          <t>1133052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703804</t>
+          <t>802147</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703804</t>
+          <t>802147</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703804</t>
+          <t>802147</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>926026</t>
+          <t>803791</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>926026</t>
+          <t>803791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>926026</t>
+          <t>803791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1629830</t>
+          <t>1605939</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1629830</t>
+          <t>1605939</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1629830</t>
+          <t>1605939</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>265032</t>
+          <t>281703</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>236010</t>
+          <t>253788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>296309</t>
+          <t>314715</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>354190</t>
+          <t>382140</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>283610</t>
+          <t>351473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>388081</t>
+          <t>407946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>619223</t>
+          <t>663843</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>546922</t>
+          <t>623613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>667310</t>
+          <t>706446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>648578</t>
+          <t>694128</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>617301</t>
+          <t>661116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>677600</t>
+          <t>722043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>723613</t>
+          <t>717412</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689722</t>
+          <t>691606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>794193</t>
+          <t>748079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1372190</t>
+          <t>1411540</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1324103</t>
+          <t>1368937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1444491</t>
+          <t>1451770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>913610</t>
+          <t>975831</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>913610</t>
+          <t>975831</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>913610</t>
+          <t>975831</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1077803</t>
+          <t>1099552</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1077803</t>
+          <t>1099552</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1077803</t>
+          <t>1099552</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1991413</t>
+          <t>2075383</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1991413</t>
+          <t>2075383</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1991413</t>
+          <t>2075383</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>862713</t>
+          <t>923114</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>669893</t>
+          <t>865964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>947806</t>
+          <t>978975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1084234</t>
+          <t>1151931</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>884215</t>
+          <t>1105992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1187018</t>
+          <t>1205191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1946946</t>
+          <t>2075045</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1673995</t>
+          <t>1999274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2093062</t>
+          <t>2152988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2573819</t>
+          <t>2583741</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2488726</t>
+          <t>2527880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2766639</t>
+          <t>2640891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2545580</t>
+          <t>2547137</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2442796</t>
+          <t>2493877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2745599</t>
+          <t>2593076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5119400</t>
+          <t>5130878</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4973284</t>
+          <t>5052935</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5392351</t>
+          <t>5206649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>72,26%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3436532</t>
+          <t>3506855</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3436532</t>
+          <t>3506855</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3436532</t>
+          <t>3506855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3629814</t>
+          <t>3699068</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3629814</t>
+          <t>3699068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3629814</t>
+          <t>3699068</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7066346</t>
+          <t>7205923</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7066346</t>
+          <t>7205923</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7066346</t>
+          <t>7205923</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
